--- a/docs/simulation-variables.xlsx
+++ b/docs/simulation-variables.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -668,6 +668,48 @@
       <c r="B27" s="4" t="inlineStr">
         <is>
           <t>FullName = '{Name}_{Variant}' — the key used by accumulators and per-species CSV columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>v10 changes (current model version)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>- Carrying capacity reframed as a shared food/resource pool that drives Tier 1 FedRate (linear: min(1, HE × food_density)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>- Soft-cap-on-births block deleted from ApplyReproduction (processing-order bug eliminated as side effect).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>- HuntingEfficiency for Tier 1 now meaningful (resource-extraction efficiency); default 1.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>- NEWBORN_CONDITION constant removed; newborns inherit parent group Condition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>- New daily CSV columns: FedRateT1, FoodDensityT1. New #config: line: model_version,v10-food-pool.</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2692,7 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Holling base efficiency at NORMAL_PREY_RATIO. Tier 1 ignored at runtime.</t>
+          <t>Dual semantic by tier (v10). Tier 2 (predators): base hunting success at NORMAL_PREY_RATIO (Holling II). Tier 1 (prey): resource-extraction efficiency from shared food pool (linear: FedRate = min(1, HE × food_density)). Default 1.0 = perfect plankton-style passive extraction. Lower values for imperfect foragers.</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3278,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Feeding satisfaction. Tier 1 = 1.0 always; Tier 2 = caught / needed.</t>
+          <t>Feeding satisfaction. Tier 1: density-dependent from shared food pool (v10) — computed in Step 2 as min(1, HuntingEfficiency × food_density). Tier 2: caught / needed (Holling II output, currently pooled across predators).</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -3364,7 +3406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3420,12 +3462,12 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>NEWBORN_CONDITION</t>
+          <t>NORMAL_PREY_RATIO</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -3435,19 +3477,19 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Condition of newborns; dilutes group average in Step 8.</t>
+          <t>Prey:predator ratio where Holling efficiency equals HuntingEfficiency.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>NORMAL_PREY_RATIO</t>
+          <t>MIN_HUNTING_SUCCESS</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -3457,19 +3499,19 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Prey:predator ratio where Holling efficiency equals HuntingEfficiency.</t>
+          <t>Floor on per-step Holling success.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>MIN_HUNTING_SUCCESS</t>
+          <t>MAX_HUNTING_SUCCESS</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -3479,19 +3521,19 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Floor on per-step Holling success.</t>
+          <t>Ceiling on per-step Holling success.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>MAX_HUNTING_SUCCESS</t>
+          <t>MIN_POPULATION_FOR_REPRODUCTION</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -3501,19 +3543,19 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Ceiling on per-step Holling success.</t>
+          <t>ApplyReproduction short-circuits below this.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>MIN_POPULATION_FOR_REPRODUCTION</t>
+          <t>STRUGGLING_REPRO_RATE</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -3523,41 +3565,41 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>ApplyReproduction short-circuits below this.</t>
+          <t>reproScale value at the ReproThreshold inflection.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>STRUGGLING_REPRO_RATE</t>
+          <t>NO_PREDATOR_PENALTY</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>EcosystemSimulator.cs</t>
+          <t>SimSpecies.cs</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>reproScale value at the ReproThreshold inflection.</t>
+          <t>Tier 1 birth multiplier when Tier 2 is absent.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>NO_PREDATOR_PENALTY</t>
+          <t>MIN_FINAL_PERF_FOR_NATURAL_DEATH</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -3567,19 +3609,19 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 birth multiplier when Tier 2 is absent.</t>
+          <t>Historical floor; not used in v9 natural-death formula.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>MIN_FINAL_PERF_FOR_NATURAL_DEATH</t>
+          <t>LETHAL_TRANSITION_WIDTH</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -3589,51 +3631,41 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Historical floor; not used in v9 natural-death formula.</t>
+          <t>°C width of cosine fade near CTmin/CTmax.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>LETHAL_TRANSITION_WIDTH</t>
+          <t>DAYS_PER_YEAR</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>SimSpecies.cs</t>
+          <t>TemperatureCalculator.cs</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>°C width of cosine fade near CTmin/CTmax.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>DAYS_PER_YEAR</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>TemperatureCalculator.cs</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
           <t>Days per simulation year for seasonal/year math.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>v10 note</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>NEWBORN_CONDITION constant removed in v10. Newborns inherit the species' current group Condition rather than entering at a fixed 0.5; the parent's Condition already encodes recent provisioning capacity via lagged drain dynamics.</t>
         </is>
       </c>
     </row>
